--- a/reports/LeetcodeDaily Report 2 year_2026-09-19.xlsx
+++ b/reports/LeetcodeDaily Report 2 year_2026-09-19.xlsx
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">

--- a/reports/LeetcodeDaily Report 2 year_2026-09-19.xlsx
+++ b/reports/LeetcodeDaily Report 2 year_2026-09-19.xlsx
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
